--- a/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
+++ b/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Enemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8D5B3F-1A70-4872-AE93-67AA64E0DD48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59F218F-E19A-40CA-97E2-DB16522BFF4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,14 +50,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>静声に熱する彷徨う者</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>微美しき魅忘の彷徨う者</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Beauteous-Bewilder Wanderer</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -75,6 +67,14 @@
   </si>
   <si>
     <t>findPlayerSEId</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="せいせい"&gt;静声&lt;/r&gt;に&lt;r="ねっ"&gt;熱&lt;/r&gt;する&lt;r="さまよ"&gt;彷徨&lt;/r&gt;う&lt;r="もの"&gt;者&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="びび"&gt;微美&lt;/r&gt;しき&lt;r="びぼう"&gt;魅忘&lt;/r&gt;の&lt;r="さまよ"&gt;彷徨&lt;/r&gt;う&lt;r="もの"&gt;者&lt;/r&gt;</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -118,8 +118,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -403,7 +406,7 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="21.75" customWidth="1"/>
+    <col min="2" max="2" width="21.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="27.25" customWidth="1"/>
     <col min="4" max="4" width="8.625" customWidth="1"/>
     <col min="5" max="5" width="7.875" customWidth="1"/>
@@ -415,20 +418,20 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
         <v>7</v>
-      </c>
-      <c r="E1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -436,15 +439,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" ht="93.75">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D3">
         <v>7</v>
@@ -456,15 +459,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" ht="93.75">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>17</v>

--- a/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
+++ b/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Enemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59F218F-E19A-40CA-97E2-DB16522BFF4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6498322C-CE65-48A9-A8CB-0721859178C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -75,6 +75,16 @@
   </si>
   <si>
     <t>&lt;r="びび"&gt;微美&lt;/r&gt;しき&lt;r="びぼう"&gt;魅忘&lt;/r&gt;の&lt;r="さまよ"&gt;彷徨&lt;/r&gt;う&lt;r="もの"&gt;者&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>沉溺寂声之徘徊者</t>
+  </si>
+  <si>
+    <t>娇美惑忘之徘徊者</t>
+  </si>
+  <si>
+    <t>nameChinese01</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -82,7 +92,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,6 +106,12 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -118,9 +134,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -403,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="21.75" style="1" customWidth="1"/>
@@ -414,7 +433,7 @@
     <col min="7" max="7" width="18.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -433,13 +452,16 @@
       <c r="F1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="93.75">
+    <row r="3" spans="1:7" ht="93.75">
       <c r="A3">
         <v>1</v>
       </c>
@@ -458,8 +480,11 @@
       <c r="F3">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="93.75">
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="93.75">
       <c r="A4">
         <v>2</v>
       </c>
@@ -478,43 +503,46 @@
       <c r="F4">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
+++ b/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Enemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6498322C-CE65-48A9-A8CB-0721859178C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0C6FA4-F6FB-4561-828D-80067AA42764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -85,6 +85,16 @@
   </si>
   <si>
     <t>nameChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>沉溺寂聲之徘徊者</t>
+  </si>
+  <si>
+    <t>嬌美惑忘之徘徊者</t>
+  </si>
+  <si>
+    <t>nameChinese02</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -92,7 +102,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,6 +122,12 @@
       <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -134,12 +150,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -422,18 +442,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="21.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="27.25" customWidth="1"/>
-    <col min="4" max="4" width="8.625" customWidth="1"/>
-    <col min="5" max="5" width="7.875" customWidth="1"/>
-    <col min="6" max="6" width="13.375" customWidth="1"/>
-    <col min="7" max="7" width="18.875" customWidth="1"/>
+    <col min="4" max="4" width="18.875" customWidth="1"/>
+    <col min="5" max="5" width="27.25" customWidth="1"/>
+    <col min="6" max="6" width="8.625" customWidth="1"/>
+    <col min="7" max="7" width="7.875" customWidth="1"/>
+    <col min="8" max="8" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -444,24 +465,28 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="93.75">
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" ht="93.75">
       <c r="A3">
         <v>1</v>
       </c>
@@ -471,20 +496,23 @@
       <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3">
         <v>7</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>8</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>9</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="93.75">
+    </row>
+    <row r="4" spans="1:8" ht="93.75">
       <c r="A4">
         <v>2</v>
       </c>
@@ -494,55 +522,58 @@
       <c r="C4" t="s">
         <v>3</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4">
         <v>17</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>18</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>19</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
+++ b/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Enemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0C6FA4-F6FB-4561-828D-80067AA42764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A179CD-87D9-4E87-9662-A5B08055A1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -96,6 +96,15 @@
   <si>
     <t>nameChinese02</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>nameSpanish</t>
+  </si>
+  <si>
+    <t>Errante que Arde en Silencio</t>
+  </si>
+  <si>
+    <t>Errante Bello del Olvido</t>
   </si>
 </sst>
 </file>
@@ -158,10 +167,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -442,19 +451,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="21.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="27.25" customWidth="1"/>
     <col min="4" max="4" width="18.875" customWidth="1"/>
-    <col min="5" max="5" width="27.25" customWidth="1"/>
-    <col min="6" max="6" width="8.625" customWidth="1"/>
-    <col min="7" max="7" width="7.875" customWidth="1"/>
-    <col min="8" max="8" width="13.375" customWidth="1"/>
+    <col min="5" max="6" width="27.25" customWidth="1"/>
+    <col min="7" max="7" width="8.625" customWidth="1"/>
+    <col min="8" max="8" width="7.875" customWidth="1"/>
+    <col min="9" max="9" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -467,26 +476,29 @@
       <c r="D1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="93.75">
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:9" ht="93.75">
       <c r="A3">
         <v>1</v>
       </c>
@@ -499,20 +511,23 @@
       <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3">
         <v>7</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>8</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="93.75">
+    <row r="4" spans="1:9" ht="93.75">
       <c r="A4">
         <v>2</v>
       </c>
@@ -525,55 +540,58 @@
       <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4">
         <v>17</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>18</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
+++ b/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Enemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A179CD-87D9-4E87-9662-A5B08055A1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F2B181-E9EF-4C81-82E3-BC0F0D46BDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -105,6 +105,15 @@
   </si>
   <si>
     <t>Errante Bello del Olvido</t>
+  </si>
+  <si>
+    <t>namePortuguese</t>
+  </si>
+  <si>
+    <t>Errante Que Arde em Silêncio</t>
+  </si>
+  <si>
+    <t>Errante Belo do Esquecimento</t>
   </si>
 </sst>
 </file>
@@ -451,19 +460,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="21.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="27.25" customWidth="1"/>
     <col min="4" max="4" width="18.875" customWidth="1"/>
-    <col min="5" max="6" width="27.25" customWidth="1"/>
-    <col min="7" max="7" width="8.625" customWidth="1"/>
-    <col min="8" max="8" width="7.875" customWidth="1"/>
-    <col min="9" max="9" width="13.375" customWidth="1"/>
+    <col min="5" max="7" width="27.25" customWidth="1"/>
+    <col min="8" max="8" width="8.625" customWidth="1"/>
+    <col min="9" max="9" width="7.875" customWidth="1"/>
+    <col min="10" max="10" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -479,26 +488,29 @@
       <c r="E1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:9" ht="93.75">
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:10" ht="93.75">
       <c r="A3">
         <v>1</v>
       </c>
@@ -514,20 +526,23 @@
       <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3">
         <v>7</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>8</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="93.75">
+    <row r="4" spans="1:10" ht="93.75">
       <c r="A4">
         <v>2</v>
       </c>
@@ -543,58 +558,69 @@
       <c r="E4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" t="s">
         <v>18</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4">
         <v>17</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>18</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>10</v>
       </c>
+      <c r="G12" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
+++ b/Assets/Originals/Excels/Enemy/EnemyInformation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Enemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F2B181-E9EF-4C81-82E3-BC0F0D46BDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47D987F-8169-4859-AA70-A9BA3B29EC4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -78,42 +78,65 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>娇美惑忘之徘徊者</t>
+  </si>
+  <si>
+    <t>nameChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>嬌美惑忘之徘徊者</t>
+  </si>
+  <si>
+    <t>nameChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>nameSpanish</t>
+  </si>
+  <si>
+    <t>Errante Bello del Olvido</t>
+  </si>
+  <si>
+    <t>namePortuguese</t>
+  </si>
+  <si>
+    <t>Errante Que Arde em Silêncio</t>
+  </si>
+  <si>
+    <t>Errante Belo do Esquecimento</t>
+  </si>
+  <si>
+    <t>&lt;r="うた"&gt;唄&lt;/r&gt;&lt;r="うた"&gt;歌&lt;/r&gt;う&lt;r="さまよ"&gt;彷徨&lt;/r&gt;う&lt;r="もの"&gt;者&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sing-song Wanderer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>咏永的彷徨者</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Canto-Llanto, el Errante</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Canto-Pranto, o Errante</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>沉溺寂声之徘徊者</t>
-  </si>
-  <si>
-    <t>娇美惑忘之徘徊者</t>
-  </si>
-  <si>
-    <t>nameChinese01</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>沉溺寂聲之徘徊者</t>
-  </si>
-  <si>
-    <t>嬌美惑忘之徘徊者</t>
-  </si>
-  <si>
-    <t>nameChinese02</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>nameSpanish</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Errante que Arde en Silencio</t>
-  </si>
-  <si>
-    <t>Errante Bello del Olvido</t>
-  </si>
-  <si>
-    <t>namePortuguese</t>
-  </si>
-  <si>
-    <t>Errante Que Arde em Silêncio</t>
-  </si>
-  <si>
-    <t>Errante Belo do Esquecimento</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -168,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -179,7 +202,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -483,16 +505,16 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
         <v>16</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="H1" t="s">
         <v>5</v>
@@ -508,7 +530,6 @@
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:10" ht="93.75">
       <c r="A3">
@@ -521,16 +542,16 @@
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
         <v>17</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="H3">
         <v>7</v>
@@ -553,16 +574,16 @@
         <v>3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
         <v>18</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="H4">
         <v>17</v>
@@ -574,53 +595,63 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" ht="75">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="G5" s="4"/>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="G12" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
